--- a/sports_forms/004_gymnastics_skills_checklist--sports_forms.xlsx
+++ b/sports_forms/004_gymnastics_skills_checklist--sports_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="7" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>roundoff</t>
+          <t>roundoff_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Roundoff</t>
+          <t>Roundoff 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -915,12 +915,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>somersault</t>
+          <t>somersault_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>somersault</t>
+          <t>Somersault 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -966,7 +966,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>handstbackspringback</t>
+          <t>handstbackspringback (2)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -984,12 +984,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>somersault</t>
+          <t>somersault_3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>somersault</t>
+          <t>Somersault 3</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>cartwheeback</t>
+          <t>cartwheeback (2)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>jumpback</t>
+          <t>jumpback_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>jumpback</t>
+          <t>Jumpback 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1266,7 +1266,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>roundoff_choices</t>
+          <t>roundoff_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1283,7 +1283,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>roundoff_choices</t>
+          <t>roundoff_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1504,7 +1504,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>somersault_choices</t>
+          <t>somersault_2_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1521,7 +1521,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>somersault_choices</t>
+          <t>somersault_2_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1538,7 +1538,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>somersault_choices</t>
+          <t>somersault_3_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1555,7 +1555,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>somersault_choices</t>
+          <t>somersault_3_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
